--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-26T17:42:14.085Z</t>
+    <t>2026-06-26T18:04:03.150Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-26T18:04:03.150Z</t>
+    <t>2026-06-26T18:42:20.695Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-26T18:42:20.695Z</t>
+    <t>2026-06-26T20:06:49.580Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-26T20:06:49.580Z</t>
+    <t>2026-06-26T20:35:38.152Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-26T20:35:38.152Z</t>
+    <t>2026-06-26T21:38:44.371Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>
